--- a/Nexora_NIST_CSF_Assessment.xlsx
+++ b/Nexora_NIST_CSF_Assessment.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Identify" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Protect" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Detect" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Respond" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Recover" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="3-Year Roadmap" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Evidence Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Identify" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Protect" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Detect" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Respond" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recover" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3-Year Roadmap" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,688 +714,1002 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NIST CSF Category</t>
+          <t>Evidence ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Control Objective</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Control (Subcategory)</t>
+          <t>Observation (current state)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Finding / Evidence</t>
+          <t>Supports controls</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+          <t>Team &amp; governance</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Physical devices and systems within the organization are inventoried.</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Nexora only keeps a spreadsheet of laptops (serial number, model, warranty). There is no CMDB, no owner per asset, no coverage of other devices and no periodic review process.</t>
+          <t>The cyber security team consists of one generalist analyst who handles incidents as they arise and reports to the IT manager.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>DE.DP-1, RS.RP-1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+          <t>Team &amp; governance</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Software platforms and applications within the organization are inventoried.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>No software/application inventory exists. Nexora relies exclusively on SaaS + Office 365, but these applications are not catalogued.</t>
+          <t>A network engineer manages the firewalls and reports to the Network Team Leader.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>DE.DP-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+          <t>Team &amp; governance</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Organizational communication and data flows are mapped.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>The IT team maintains up-to-date network diagrams that include the cloud environment. Recommendation: extend them with data flows to key SaaS providers (e.g. Horizon Labs).</t>
+          <t>The newly hired cyber security consultant also reports to the IT manager; cyber has no executive-level reporting line.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ID.GV-4, RC.CO-3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+          <t>Team &amp; governance</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>External information systems are catalogued.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SaaS instances are not catalogued or classified by sensitivity/criticality. No inventory of third-party suppliers (no TPRM process).</t>
+          <t>The CEO has a clear business strategy.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ID.BE-3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+          <t>Team &amp; governance</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Resources (e.g., hardware, devices, data and software) are prioritized based on their classification, criticality and business value.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>There is no information classification scheme, so assets cannot be prioritised by sensitivity, criticality or business value.</t>
+          <t>Cyber security roles and responsibilities are not defined; they are informally assigned to the IT team.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-6, ID.GV-2, PR.AT-5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+          <t>Team &amp; governance</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity roles and responsibilities for the entire workforce and third-party stakeholders (e.g., suppliers, customers, partners) are established.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Cyber security roles and responsibilities are not defined; they are informally assigned to the IT team. There is no information security policy.</t>
+          <t>There is no cyber security strategy.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ID.GV-4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Business Environment</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+          <t>Asset management</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>The organization’s role in the supply chain is identified and communicated.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>No third-party risk management. Suppliers are not mapped or classified, including the critical SaaS provider Horizon Labs.</t>
+          <t>IT keeps a spreadsheet of laptops with serial number, model and warranty details.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Business Environment</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+          <t>Asset management</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>The organization’s place in critical infrastructure and its industry sector is identified and communicated.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>No evidence on whether Nexora is considered critical infrastructure. To be confirmed with the CEO/legal and documented in the information security policy.</t>
+          <t>The organisation uses Microsoft 365 and relies exclusively on SaaS applications (no in-house software development).</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-2, ID.AM-4, PR.DS-7, PR.IP-2, PR.PT-3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Business Environment</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+          <t>Asset management</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Priorities for organizational mission, objectives and activities are established and communicated.</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>The CEO has a clear business strategy for the business.</t>
+          <t>All data is hosted in Microsoft Azure / Microsoft 365; there are no on-premise servers.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>PR.DS-1, PR.DS-4, PR.MA-1, PR.MA-2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Business Environment</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+          <t>Asset management</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Dependencies and critical functions for delivery of critical services are established.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Partially met: business continuity and DR plans exist and are documented, but key critical services/applications (e.g. Horizon Labs) are not formally inventoried and classified.</t>
+          <t>All laptops are imaged with a Secure Operating Environment (SOE) running the latest Windows version.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Business Environment</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+          <t>BCP / DR</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Resilience requirements to support delivery of critical services are established.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Partially met: BCP/DR are tested internally, but there is no due diligence (SLA, SOC 2 reports, BCP) on critical third-party services such as Horizon Labs and Microsoft Azure.</t>
+          <t>IT conducts regular disaster recovery testing.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>ID.BE-4, ID.BE-5, PR.DS-4, PR.IP-10, RC.RP-1, RC.IM-1, RC.IM-2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+          <t>BCP / DR</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Organizational information security policy is established.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Only one generic IT policy exists. There is no formal information security policy.</t>
+          <t>IT has clear, documented business continuity plans.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>ID.BE-4, ID.BE-5, PR.DS-4, PR.IP-9, RC.CO-1, RC.CO-2, RC.CO-3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+          <t>BCP / DR</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Information security roles and responsibilities are coordinated and aligned with internal roles and external partners.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Information security roles are not documented or communicated to internal or external stakeholders.</t>
+          <t>Regular backups are taken and tested periodically.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+          <t>Vulnerability management</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Legal and regulatory requirements regarding cybersecurity, including privacy and civil liberties obligations, are understood and managed.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Legal, regulatory and privacy obligations for information security are not documented. No data governance policies are in place.</t>
+          <t>A Qualys vulnerability scanner has been purchased but is only used ad hoc.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>ID.RA-1, PR.IP-12, DE.CM-8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+          <t>Vulnerability management</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Governance and risk management processes address cybersecurity risk.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>There is no technology or cyber risk process and no cyber security strategy. Cyber reports to the IT manager; there is no board-level oversight of cyber risk.</t>
+          <t>There is no formal vulnerability management program.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>ID.RA-1, ID.RA-2, PR.IP-12, RS.MI-3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+          <t>Vulnerability management</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Asset vulnerabilities are identified and documented.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Qualys is used ad hoc only. A large number of high/severe vulnerabilities are reported but not formally analysed, documented or tracked.</t>
+          <t>Qualys reports a large number of high and severe vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>ID.RA-1, PR.IP-12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+          <t>Risk management</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Threat and vulnerability information is received from information sharing forums and sources.</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>No formal vulnerability management program and no threat intelligence subscriptions.</t>
+          <t>A risk team exists but only performs financial risk activities.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>ID.RA-4, ID.RM-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+          <t>Risk management</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Threats, both internal and external, are identified and documented.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>No cyber threat assessments have been performed; threat actors have not been identified or documented.</t>
+          <t>There is no technology or cyber risk process.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>ID.GV-4, ID.RA-3, ID.RA-4, ID.RA-5, ID.RA-6, ID.RM-1, ID.RM-2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+          <t>Third-party risk</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Potential business impacts and likelihoods are identified.</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>The risk team only performs financial risk activities. No cyber risk assessments considering impact and likelihood.</t>
+          <t>No third-party risk management is performed.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-4, ID.BE-1, ID.BE-5, PR.AT-3, DE.CM-6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+          <t>Third-party risk</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Threats, vulnerabilities, likelihoods and impacts are used to determine risk.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>No cyber risk assessment process exists to combine threats, vulnerabilities, likelihood and impact.</t>
+          <t>Contracts are reviewed by procurement and finance only, not by IT/security.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>ID.GV-2, PR.AT-3, DE.CM-6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+          <t>Identity &amp; access</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Risk responses are identified and prioritized.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Without cyber risk assessments, risk responses are not identified or prioritised.</t>
+          <t>Microsoft Active Directory is used to manage users and groups.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The organization’s priorities, constraints, risk tolerances, and assumptions are established and used to support operational risk decisions.</t>
+          <t>Identity &amp; access</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Risk management processes are established, managed and agreed to by organizational stakeholders.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>The risk management process covers financial risk only. No cyber risk management process endorsed by senior management.</t>
+          <t>There is no privileged access management (PAM) solution.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-1, PR.AT-2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>E23</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>The organization’s priorities, constraints, risk tolerances, and assumptions are established and used to support operational risk decisions.</t>
+          <t>Identity &amp; access</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Organizational risk tolerance is determined and clearly expressed.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>No cyber risk appetite statement has been defined or approved.</t>
+          <t>The admin account password is shared among several senior IT staff.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-1, PR.AC-4, PR.AT-2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The organization’s priorities, constraints, risk tolerances, and assumptions are established and used to support operational risk decisions.</t>
+          <t>Identity &amp; access</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>The organization’s determination of risk tolerance is informed by its role in critical infrastructure and sector-specific risk analysis.</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Depends on whether the organisation is critical infrastructure (see row 9). Risk tolerance must be defined once a cyber risk process exists.</t>
+          <t>Access to resources is granted upon request.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Identity &amp; access</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Two-factor authentication is not used for login.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-1, PR.AC-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>E26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Identity &amp; access</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Complex login passwords are enforced.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>E27</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Identity &amp; access</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Employees use a VPN for remote access when required.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-3, PR.DS-2, PR.PT-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Network security</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Palo Alto next-generation firewalls are in place, configured by the network team.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-5, PR.PT-3, PR.PT-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>E29</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Network security</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Firewalls are audited every year by the network team.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>PR.PT-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>E30</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Network security</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Firewalls receive regular updates.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>PR.PT-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>E31</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Network security</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>IT maintains up-to-date network diagrams that include the cloud environment.</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>E32</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Network security</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>The network is segmented using VLANs.</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-5, PR.PT-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>E33</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Physical security</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>The facility is highly secure with state-of-the-art CCTV coverage; physical security is taken very seriously.</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-2, PR.IP-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>E34</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Physical security</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Extensive vetting is performed for all employees.</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>E35</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Physical security</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Research labs and physical facilities are monitored 24/7.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>PR.AC-2, PR.IP-5, DE.CM-2, DE.CM-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Data security</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>There is no Data Loss Prevention (DLP) solution.</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>PR.DS-1, PR.DS-2, PR.DS-5, PR.PT-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>E37</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Data security</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>The key critical application is a SaaS service provided by Horizon Labs (fictional third party).</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-4, ID.BE-1, ID.BE-4, ID.BE-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Only one generic IT policy exists.</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>ID.GV-1, PR.IP-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>E39</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>There is no formal information security policy.</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-6, ID.GV-1, PR.IP-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>There are no data governance policies and no information classification.</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>ID.AM-5, ID.GV-3, PR.DS-1, PR.DS-2, PR.DS-3, PR.IP-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Detection &amp; response</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>There is no detection or incident response capability.</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-9, PR.IP-10, DE.AE-2, DE.AE-4, DE.AE-5, DE.DP-2, DE.DP-3, DE.DP-4, DE.DP-5, RS.RP-1, RS.CO-1, RS.CO-2, RS.CO-3, RS.CO-4, RS.CO-5, RS.AN-2, RS.AN-3, RS.AN-4, RS.MI-1, RS.MI-2, RS.IM-1, RS.IM-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>E42</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Detection &amp; response</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>IT responds to alerts from the anti-virus (Microsoft Defender).</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>DE.AE-2, DE.CM-4, DE.CM-5, RS.AN-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>E43</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Detection &amp; response</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>No SIEM is in place.</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>PR.PT-1, DE.AE-1, DE.AE-3, DE.CM-1, DE.CM-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>E44</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>All employees complete a one-off induction web module with basic cyber security instructions.</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>PR.AT-1, PR.AT-4</t>
         </is>
       </c>
     </row>
@@ -1409,985 +1724,940 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>CSF ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>NIST CSF Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Control Objective</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Control (Subcategory)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Finding / Evidence</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>ID.AM-1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Identities and credentials are managed for authorized devices and users.</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Active Directory and complex passwords are used, but there is no MFA, no PAM, the admin password is shared among senior IT staff and there are no regular user access reviews.</t>
+          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Physical devices and systems within the organization are inventoried.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Nexora only keeps a spreadsheet of laptops (serial number, model, warranty). There is no CMDB, no owner per asset, no coverage of other devices and no periodic review process.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>E07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>ID.AM-2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Physical access to assets is managed and protected.</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Highly secure facility: state-of-the-art CCTV everywhere and 24/7 monitoring of research labs and physical facilities.</t>
+          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Software platforms and applications within the organization are inventoried.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>No software/application inventory exists. Nexora relies exclusively on SaaS + Office 365, but these applications are not catalogued.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>E08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>ID.AM-3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Remote access is managed.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>VPN is used for remote access, but without two-factor authentication. The process for contractor/third-party access is not defined.</t>
+          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Organizational communication and data flows are mapped.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>The IT team maintains up-to-date network diagrams that include the cloud environment. Recommendation: extend them with data flows to key SaaS providers (e.g. Horizon Labs).</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>E31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>ID.AM-4</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Access permissions are managed, incorporating the principles of least privilege and separation of duties.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Access is granted on request without least-privilege/segregation-of-duties checks or periodic reviews. Shared admin account breaks accountability.</t>
+          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>External information systems are catalogued.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>SaaS instances are not catalogued or classified by sensitivity/criticality. No inventory of third-party suppliers (no TPRM process).</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>E08, E19, E37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>ID.AM-5</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Network integrity is protected, incorporating network segregation where appropriate.</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>The network is segmented using VLANs and protected by Palo Alto next-generation firewalls.</t>
+          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Resources (e.g., hardware, devices, data and software) are prioritized based on their classification, criticality and business value.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>There is no information classification scheme, so assets cannot be prioritised by sensitivity, criticality or business value.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>E40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Awareness Training</t>
+          <t>ID.AM-6</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>All users are informed and trained.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Only a one-off induction web module with basic cyber instructions. No regular, mandatory awareness training or phishing simulations; contractors not covered.</t>
+          <t>The data, personnel, devices, systems, and facilities that enable the organization to achieve business purposes are identified and managed consistent with their relative importance to business objectives and the organization’s risk strategy.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Cybersecurity roles and responsibilities for the entire workforce and third-party stakeholders (e.g., suppliers, customers, partners) are established.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Cyber security roles and responsibilities are not defined; they are informally assigned to the IT team. There is no information security policy.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>E05, E39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Awareness Training</t>
+          <t>ID.BE-1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+          <t>Business Environment</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Privileged users understand roles and responsibilities.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>No privileged access management solution or process. Admin password is shared.</t>
+          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>The organization’s role in the supply chain is identified and communicated.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>No third-party risk management. Suppliers are not mapped or classified, including the critical SaaS provider Horizon Labs.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>E19, E37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Awareness Training</t>
+          <t>ID.BE-2</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+          <t>Business Environment</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Third-party stakeholders (e.g., suppliers, customers, partners) understand roles and responsibilities.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Contracts are reviewed by procurement and finance only, without security clauses. No security assessments before onboarding suppliers.</t>
+          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>The organization’s place in critical infrastructure and its industry sector is identified and communicated.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>No evidence on whether Nexora is considered critical infrastructure. To be confirmed with the CEO/legal and documented in the information security policy.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>No evidence (absence)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Awareness Training</t>
+          <t>ID.BE-3</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+          <t>Business Environment</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Senior executives understand roles and responsibilities.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>No evidence of mandatory security training for executives or the board; board cyber responsibilities are not defined.</t>
+          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Priorities for organizational mission, objectives and activities are established and communicated.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>The CEO has a clear business strategy for the business.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>E04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Awareness Training</t>
+          <t>ID.BE-4</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+          <t>Business Environment</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Physical and information security personnel understand roles and responsibilities.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Cyber security roles and responsibilities have not been defined or communicated to staff, including physical security staff.</t>
+          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Dependencies and critical functions for delivery of critical services are established.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Partially met: business continuity and DR plans exist and are documented, but key critical services/applications (e.g. Horizon Labs) are not formally inventoried and classified.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>E11, E12, E37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Data Security</t>
+          <t>ID.BE-5</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+          <t>Business Environment</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Data-at-rest is protected.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Data resides in Azure/Office 365 (encryption at rest by default - to verify), but no data discovery, classification or labelling and no DLP.</t>
+          <t>The organization’s mission, objectives, stakeholders, and activities are understood and prioritized; this information is used to inform cybersecurity roles, responsibilities, and risk management decisions.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Resilience requirements to support delivery of critical services are established.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Partially met: BCP/DR are tested internally, but there is no due diligence (SLA, SOC 2 reports, BCP) on critical third-party services such as Horizon Labs and Microsoft Azure.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>E11, E12, E19, E37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Data Security</t>
+          <t>ID.GV-1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Data-in-transit is protected.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Transit encryption is provided by SaaS/VPN by default (to verify), but there is no data classification, no DLP and no control over USB copying.</t>
+          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Organizational information security policy is established.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Only one generic IT policy exists. There is no formal information security policy.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>E38, E39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Data Security</t>
+          <t>ID.GV-2</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Assets are formally managed throughout removal, transfers and disposition.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>No documented process for offboarding assets or data disposal (no data governance policies).</t>
+          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Information security roles and responsibilities are coordinated and aligned with internal roles and external partners.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Information security roles are not documented or communicated to internal or external stakeholders.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>E05, E20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Data Security</t>
+          <t>ID.GV-3</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Adequate capacity to ensure availability is maintained.</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Documented and regularly tested BCP/DR plans; services hosted in Azure/SaaS provide high availability. Confirm DoS protection for critical services.</t>
+          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Legal and regulatory requirements regarding cybersecurity, including privacy and civil liberties obligations, are understood and managed.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Legal, regulatory and privacy obligations for information security are not documented. No data governance policies are in place.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>E40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Data Security</t>
+          <t>ID.GV-4</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Protections against data leaks are implemented.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>No Data Loss Prevention (DLP) solution or program in place.</t>
+          <t>The policies, procedures, and processes to manage and monitor the organization’s regulatory, legal, risk, environmental, and operational requirements are understood and inform the management of cybersecurity risk.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Governance and risk management processes address cybersecurity risk.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>There is no technology or cyber risk process and no cyber security strategy. Cyber reports to the IT manager; there is no board-level oversight of cyber risk.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>E03, E06, E18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Data Security</t>
+          <t>ID.RA-1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Integrity checking mechanisms are used to verify software, firmware and information integrity.</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Integrity checking is built into modern software/firmware; considered met.</t>
+          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Asset vulnerabilities are identified and documented.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Qualys is used ad hoc only. A large number of high/severe vulnerabilities are reported but not formally analysed, documented or tracked.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>E14, E15, E16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Data Security</t>
+          <t>ID.RA-2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>The development and testing environment(s) are separate from the production environment.</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Nexora does not perform software development; it relies exclusively on SaaS applications.</t>
+          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Threat and vulnerability information is received from information sharing forums and sources.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>No formal vulnerability management program and no threat intelligence subscriptions.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>E15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Information Protection Processes and Procedures</t>
+          <t>ID.RA-3</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>A baseline configuration of information technology/industrial control systems is created and maintained.</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>The IT team uses a Secure Operating Environment (SOE) image with the latest Windows version for all laptops.</t>
+          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Threats, both internal and external, are identified and documented.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>No cyber threat assessments have been performed; threat actors have not been identified or documented.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>E18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Information Protection Processes and Procedures</t>
+          <t>ID.RA-4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>A system development life cycle (SDLC) to manage systems is implemented.</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>No software development activities (SaaS only).</t>
+          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Potential business impacts and likelihoods are identified.</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>The risk team only performs financial risk activities. No cyber risk assessments considering impact and likelihood.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>E17, E18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Information Protection Processes and Procedures</t>
+          <t>ID.RA-5</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Configuration change control processes are in place.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>No evidence of a documented change management process with approvals. To be implemented and documented.</t>
+          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Threats, vulnerabilities, likelihoods and impacts are used to determine risk.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>No cyber risk assessment process exists to combine threats, vulnerabilities, likelihood and impact.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>E18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Information Protection Processes and Procedures</t>
+          <t>ID.RA-6</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Backups of information are conducted, maintained and tested periodically.</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Regular backups are taken and tested periodically.</t>
+          <t>The organization understands the cybersecurity risk to organizational operations (including mission, functions, image, or reputation), organizational assets, and individuals.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Risk responses are identified and prioritized.</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Without cyber risk assessments, risk responses are not identified or prioritised.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>E18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Information Protection Processes and Procedures</t>
+          <t>ID.RM-1</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Policy and regulations regarding the physical operating environment for organizational assets are met.</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Physical security is taken very seriously: CCTV, 24/7 monitoring and strict facility controls.</t>
+          <t>The organization’s priorities, constraints, risk tolerances, and assumptions are established and used to support operational risk decisions.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Risk management processes are established, managed and agreed to by organizational stakeholders.</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>The risk management process covers financial risk only. No cyber risk management process endorsed by senior management.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>E17, E18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Information Protection Processes and Procedures</t>
+          <t>ID.RM-2</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Data is destroyed according to policy.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>No data governance policy or documented data disposal procedure.</t>
+          <t>The organization’s priorities, constraints, risk tolerances, and assumptions are established and used to support operational risk decisions.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Organizational risk tolerance is determined and clearly expressed.</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>No cyber risk appetite statement has been defined or approved.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>E18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Information Protection Processes and Procedures</t>
+          <t>ID.RM-3</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Protection processes are continuously improved.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>No information security policies or processes exist, so there is no continuous improvement of protection processes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Information Protection Processes and Procedures</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Effectiveness of protection technologies is shared with appropriate parties.</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>No participation in information sharing with industry partners.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Information Protection Processes and Procedures</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Response plans (incident response and business continuity) and recovery plans (incident recovery and disaster recovery) are in place and managed.</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Partially met: BCP and DR plans exist, but there is no cyber security incident response plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Information Protection Processes and Procedures</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Response and recovery plans are tested.</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Partially met: DR is tested regularly, but incident response is not tested (no IR plan exists).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Information Protection Processes and Procedures</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Cybersecurity is included in human resources practices. (e.g., deprovisioning, personnel screening)</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Extensive vetting is performed for all employees. To confirm: timely disabling of accounts during offboarding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Information Protection Processes and Procedures</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>A vulnerability management plan is developed and implemented.</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Qualys is purchased but used ad hoc; no formal vulnerability management program; large backlog of high/severe vulnerabilities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance and repairs of industrial control and information system components is performed consistent with policies and procedures.</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance and repair of organizational assets is performed and logged in a timely manner, with approved and controlled tools.</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>No physical servers - all systems are in Azure/SaaS. Laptop warranty details are tracked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance and repairs of industrial control and information system components is performed consistent with policies and procedures.</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Remote maintenance of organizational assets is approved, logged and performed in a manner that prevents unauthorized access.</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>No on-premise servers maintained by third parties.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Protective Technology</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Audit/log records are determined, documented, implemented and reviewed in accordance with policy.</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>No SIEM and no evidence of audit logs being collected, protected and reviewed (firewalls, Windows, Azure/O365).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Protective Technology</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Removable media is protected and its use restricted according to policy.</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>No removable media policy or technical restriction of USB devices (no DLP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Protective Technology</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Access to systems and assets is controlled, incorporating the principle of least functionality.</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>SaaS/cloud model separates functions by service (O365, Horizon Labs, dedicated firewalls). Confirm for any remaining internal systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Protective Technology</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Communications and control networks are protected.</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Palo Alto NGFW (regularly updated, audited yearly), VLAN segmentation and VPN for remote access.</t>
+          <t>The organization’s priorities, constraints, risk tolerances, and assumptions are established and used to support operational risk decisions.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>The organization’s determination of risk tolerance is informed by its role in critical infrastructure and sector-specific risk analysis.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Depends on whether the organisation is critical infrastructure (see row 9). Risk tolerance must be defined once a cyber risk process exists.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>No evidence (absence)</t>
         </is>
       </c>
     </row>
@@ -2402,526 +2672,1347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>CSF ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>NIST CSF Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Control Objective</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Control (Subcategory)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Finding / Evidence</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Anomalies and Events</t>
+          <t>PR.AC-1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+          <t>Access Control</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>A baseline of network operations and expected data flows for users and systems is established and managed.</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>No SIEM in place, so no baseline of normal network/user activity.</t>
+          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Identities and credentials are managed for authorized devices and users.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Active Directory and complex passwords are used, but there is no MFA, no PAM, the admin password is shared among senior IT staff and there are no regular user access reviews.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>E21, E22, E23, E25, E26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Anomalies and Events</t>
+          <t>PR.AC-2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+          <t>Access Control</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Detected events are analyzed to understand attack targets and methods.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>No detection capability. The IT team only reacts to Microsoft Defender antivirus alerts.</t>
+          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Physical access to assets is managed and protected.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Highly secure facility: state-of-the-art CCTV everywhere and 24/7 monitoring of research labs and physical facilities.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>E33, E35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Anomalies and Events</t>
+          <t>PR.AC-3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+          <t>Access Control</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Event data are aggregated and correlated from multiple sources and sensors.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>No SIEM; event data is not aggregated or correlated.</t>
+          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Remote access is managed.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>VPN is used for remote access, but without two-factor authentication. The process for contractor/third-party access is not defined.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>E25, E27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Anomalies and Events</t>
+          <t>PR.AC-4</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+          <t>Access Control</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Impact of events is determined.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>No process to classify events by impact/criticality.</t>
+          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Access permissions are managed, incorporating the principles of least privilege and separation of duties.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Access is granted on request without least-privilege/segregation-of-duties checks or periodic reviews. Shared admin account breaks accountability.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>E23, E24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Anomalies and Events</t>
+          <t>PR.AC-5</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+          <t>Access Control</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Incident alert thresholds are established.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>No alert thresholds or escalation points defined.</t>
+          <t>Access to assets and associated facilities is limited to authorized users, processes, or devices, and to authorized activities and transactions.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Network integrity is protected, incorporating network segregation where appropriate.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>The network is segmented using VLANs and protected by Palo Alto next-generation firewalls.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>E28, E32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.AT-1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Awareness Training</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>The network is monitored to detect potential cybersecurity events.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Network traffic is not monitored for malicious activity (no SIEM/SOC).</t>
+          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>All users are informed and trained.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Only a one-off induction web module with basic cyber instructions. No regular, mandatory awareness training or phishing simulations; contractors not covered.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>E44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.AT-2</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Awareness Training</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>The physical environment is monitored to detect potential cybersecurity events.</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>24/7 monitoring of research labs and physical facilities with CCTV. Recommendation: integrate physical alerts into security monitoring.</t>
+          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Privileged users understand roles and responsibilities.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>No privileged access management solution or process. Admin password is shared.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>E22, E23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.AT-3</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Awareness Training</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Personnel activity is monitored to detect potential cybersecurity events.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Only physical monitoring. No monitoring of user activity in IT systems (no SIEM/UEBA).</t>
+          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Third-party stakeholders (e.g., suppliers, customers, partners) understand roles and responsibilities.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Contracts are reviewed by procurement and finance only, without security clauses. No security assessments before onboarding suppliers.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>E19, E20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.AT-4</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Awareness Training</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Malicious code is detected.</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft Defender is in place as anti-malware. To confirm coverage of all endpoints.</t>
+          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Senior executives understand roles and responsibilities.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>No evidence of mandatory security training for executives or the board; board cyber responsibilities are not defined.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>E44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.AT-5</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Awareness Training</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Unauthorized mobile code is detected.</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft Defender scans files. To confirm that email scanning (Defender for Office 365) is enabled.</t>
+          <t>The organization’s personnel and partners are provided cybersecurity awareness education and are adequately trained to perform their information security-related duties and responsibilities consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Physical and information security personnel understand roles and responsibilities.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Cyber security roles and responsibilities have not been defined or communicated to staff, including physical security staff.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>E05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.DS-1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>External service provider activity is monitored to detect potential cybersecurity events.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>No TPRM; contracts do not require suppliers to notify breaches.</t>
+          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Data-at-rest is protected.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Data resides in Azure/Office 365 (encryption at rest by default - to verify), but no data discovery, classification or labelling and no DLP.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>E09, E36, E40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.DS-2</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Monitoring for unauthorized personnel, connections, devices and software is performed.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>No evidence of controls restricting unregistered devices or USB drives. To confirm.</t>
+          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Data-in-transit is protected.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Transit encryption is provided by SaaS/VPN by default (to verify), but there is no data classification, no DLP and no control over USB copying.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>E27, E36, E40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Security Continuous Monitoring</t>
+          <t>PR.DS-3</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Vulnerability scans are performed.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Qualys scans are only run ad hoc; scan frequency and coverage are not defined.</t>
+          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Assets are formally managed throughout removal, transfers and disposition.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>No documented process for offboarding assets or data disposal (no data governance policies).</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>E40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Detection Processes</t>
+          <t>PR.DS-4</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Roles and responsibilities for detection are well defined to ensure accountability.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>One generalist analyst reporting to the IT manager; detection &amp; response roles not defined; no MSSP.</t>
+          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Adequate capacity to ensure availability is maintained.</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Documented and regularly tested BCP/DR plans; services hosted in Azure/SaaS provide high availability. Confirm DoS protection for critical services.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>E09, E11, E12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Detection Processes</t>
+          <t>PR.DS-5</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Detection activities comply with all applicable requirements.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>No detection capability, so compliance with applicable requirements cannot be demonstrated.</t>
+          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Protections against data leaks are implemented.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>No Data Loss Prevention (DLP) solution or program in place.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>E36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Detection Processes</t>
+          <t>PR.DS-6</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Detection processes are tested.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>No detection use cases, cyber drills or penetration tests.</t>
+          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Integrity checking mechanisms are used to verify software, firmware and information integrity.</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Integrity checking is built into modern software/firmware; considered met.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Template default</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Detection Processes</t>
+          <t>PR.DS-7</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+          <t>Data Security</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Event detection information is communicated to appropriate parties.</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>No documented communication paths or escalation points for detected events.</t>
+          <t>Information and records (data) are managed consistent with the organization’s risk strategy to protect the confidentiality, integrity, and availability of information.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>The development and testing environment(s) are separate from the production environment.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Nexora does not perform software development; it relies exclusively on SaaS applications.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>E08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Detection Processes</t>
+          <t>PR.IP-1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+          <t>Information Protection Processes and Procedures</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Detection processes are continuously improved.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>No lessons-learned or continuous improvement process for detection.</t>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>A baseline configuration of information technology/industrial control systems is created and maintained.</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>The IT team uses a Secure Operating Environment (SOE) image with the latest Windows version for all laptops.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-2</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>A system development life cycle (SDLC) to manage systems is implemented.</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>No software development activities (SaaS only).</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-3</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Configuration change control processes are in place.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>No evidence of a documented change management process with approvals. To be implemented and documented.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>No evidence (absence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-4</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Backups of information are conducted, maintained and tested periodically.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Regular backups are taken and tested periodically.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-5</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Policy and regulations regarding the physical operating environment for organizational assets are met.</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Physical security is taken very seriously: CCTV, 24/7 monitoring and strict facility controls.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>E33, E35</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-6</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Data is destroyed according to policy.</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>No data governance policy or documented data disposal procedure.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-7</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Protection processes are continuously improved.</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>No information security policies or processes exist, so there is no continuous improvement of protection processes.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>E38, E39</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-8</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Effectiveness of protection technologies is shared with appropriate parties.</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>No participation in information sharing with industry partners.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>No evidence (absence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-9</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Response plans (incident response and business continuity) and recovery plans (incident recovery and disaster recovery) are in place and managed.</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Partially met: BCP and DR plans exist, but there is no cyber security incident response plan.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>E12, E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-10</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Response and recovery plans are tested.</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Partially met: DR is tested regularly, but incident response is not tested (no IR plan exists).</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>E11, E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-11</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Cybersecurity is included in human resources practices. (e.g., deprovisioning, personnel screening)</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Extensive vetting is performed for all employees. To confirm: timely disabling of accounts during offboarding.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>E34</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>PR.IP-12</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Information Protection Processes and Procedures</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Security policies (that address purpose, scope, roles, responsibilities, management commitment, and coordination among organizational entities), processes, and procedures are maintained and used to manage protection of information systems and assets.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>A vulnerability management plan is developed and implemented.</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Qualys is purchased but used ad hoc; no formal vulnerability management program; large backlog of high/severe vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>E14, E15, E16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>PR.MA-1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance and repairs of industrial control and information system components is performed consistent with policies and procedures.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance and repair of organizational assets is performed and logged in a timely manner, with approved and controlled tools.</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>No physical servers - all systems are in Azure/SaaS. Laptop warranty details are tracked.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>PR.MA-2</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance and repairs of industrial control and information system components is performed consistent with policies and procedures.</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Remote maintenance of organizational assets is approved, logged and performed in a manner that prevents unauthorized access.</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>No on-premise servers maintained by third parties.</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>PR.PT-1</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Protective Technology</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Audit/log records are determined, documented, implemented and reviewed in accordance with policy.</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>No SIEM and no evidence of audit logs being collected, protected and reviewed (firewalls, Windows, Azure/O365).</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>E43</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>PR.PT-2</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Protective Technology</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Removable media is protected and its use restricted according to policy.</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>No removable media policy or technical restriction of USB devices (no DLP).</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>PR.PT-3</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Protective Technology</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Access to systems and assets is controlled, incorporating the principle of least functionality.</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>SaaS/cloud model separates functions by service (O365, Horizon Labs, dedicated firewalls). Confirm for any remaining internal systems.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>E08, E28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>PR.PT-4</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Protective Technology</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Technical security solutions are managed to ensure the security and resilience of systems and assets, consistent with related policies, procedures, and agreements.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Communications and control networks are protected.</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Palo Alto NGFW (regularly updated, audited yearly), VLAN segmentation and VPN for remote access.</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>E27, E28, E29, E30, E32</t>
         </is>
       </c>
     </row>
@@ -2936,445 +4027,718 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>CSF ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>NIST CSF Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Control Objective</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Control (Subcategory)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Finding / Evidence</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Response Planning</t>
+          <t>DE.AE-1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Response processes and procedures are executed and maintained, to ensure timely response to detected cybersecurity events.</t>
+          <t>Anomalies and Events</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Response plan is executed during or after an event.</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>No cyber security incident response plan. The analyst responds to incidents 'as they come'.</t>
+          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>A baseline of network operations and expected data flows for users and systems is established and managed.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>No SIEM in place, so no baseline of normal network/user activity.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>E43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>DE.AE-2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+          <t>Anomalies and Events</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Personnel know their roles and order of operations when a response is needed.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>No IR plan with contact details and escalation points; nothing tested.</t>
+          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Detected events are analyzed to understand attack targets and methods.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>No detection capability. The IT team only reacts to Microsoft Defender antivirus alerts.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>E41, E42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>DE.AE-3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+          <t>Anomalies and Events</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Events are reported consistent with established criteria.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>No defined reporting thresholds; incident response process is immature/ad hoc.</t>
+          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Event data are aggregated and correlated from multiple sources and sensors.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>No SIEM; event data is not aggregated or correlated.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>E43</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>DE.AE-4</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+          <t>Anomalies and Events</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Information is shared consistent with response plans.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>No escalation points, including when to involve law enforcement.</t>
+          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Impact of events is determined.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>No process to classify events by impact/criticality.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>DE.AE-5</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+          <t>Anomalies and Events</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Coordination with stakeholders occurs consistent with response plans.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>No documented coordination with other teams for escalated incidents.</t>
+          <t>Anomalous activity is detected in a timely manner and the potential impact of events is understood.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Incident alert thresholds are established.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>No alert thresholds or escalation points defined.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>DE.CM-1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Voluntary information sharing occurs with external stakeholders to achieve broader cybersecurity situational awareness.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>No voluntary information sharing with industry peers.</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>The network is monitored to detect potential cybersecurity events.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Network traffic is not monitored for malicious activity (no SIEM/SOC).</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>E43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>DE.CM-2</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Notifications from detection systems are investigated.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Only antivirus alerts are investigated by IT; no defined process and no 24/7 coverage.</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>The physical environment is monitored to detect potential cybersecurity events.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>24/7 monitoring of research labs and physical facilities with CCTV. Recommendation: integrate physical alerts into security monitoring.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>E35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>DE.CM-3</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>The impact of the incident is understood.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Impact/criticality of incidents is not documented.</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Personnel activity is monitored to detect potential cybersecurity events.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Only physical monitoring. No monitoring of user activity in IT systems (no SIEM/UEBA).</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>E35, E43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>DE.CM-4</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Forensics are performed.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>No digital forensics capability (people, skills or tools).</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Malicious code is detected.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft Defender is in place as anti-malware. To confirm coverage of all endpoints.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>E42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>DE.CM-5</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Incidents are categorized consistent with response plans.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>No IR plan to categorise and prioritise incidents.</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Unauthorized mobile code is detected.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft Defender scans files. To confirm that email scanning (Defender for Office 365) is enabled.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>E42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Mitigation</t>
+          <t>DE.CM-6</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Activities are performed to prevent expansion of an event, mitigate its effects and eradicate the incident.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Incidents are contained.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>No IR plan following a standard (e.g. NIST SP 800-61 / SANS) for containment.</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>External service provider activity is monitored to detect potential cybersecurity events.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>No TPRM; contracts do not require suppliers to notify breaches.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>E19, E20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mitigation</t>
+          <t>DE.CM-7</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Activities are performed to prevent expansion of an event, mitigate its effects and eradicate the incident.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Incidents are mitigated.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>No IR plan following a standard for mitigation and eradication.</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Monitoring for unauthorized personnel, connections, devices and software is performed.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>No evidence of controls restricting unregistered devices or USB drives. To confirm.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>No evidence (absence)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Mitigation</t>
+          <t>DE.CM-8</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Activities are performed to prevent expansion of an event, mitigate its effects and eradicate the incident.</t>
+          <t>Security Continuous Monitoring</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Newly identified vulnerabilities are mitigated or documented as accepted risk.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>No vulnerability management program to handle newly discovered vulnerabilities (incl. zero days) or document accepted risk.</t>
+          <t>The information system and assets are monitored at discrete intervals to identify cybersecurity events and verify the effectiveness of protective measures.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Vulnerability scans are performed.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Qualys scans are only run ad hoc; scan frequency and coverage are not defined.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>E14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Improvements</t>
+          <t>DE.DP-1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Organizational response activities are improved by incorporating lessons learned from current and previous detection/response activities.</t>
+          <t>Detection Processes</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Response plans incorporate lessons learned.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>No IR plan, so no lessons-learned step.</t>
+          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Roles and responsibilities for detection are well defined to ensure accountability.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>One generalist analyst reporting to the IT manager; detection &amp; response roles not defined; no MSSP.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>E01, E02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Improvements</t>
+          <t>DE.DP-2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Organizational response activities are improved by incorporating lessons learned from current and previous detection/response activities.</t>
+          <t>Detection Processes</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Response strategies are updated.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>No IR plan to test and update.</t>
+          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Detection activities comply with all applicable requirements.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>No detection capability, so compliance with applicable requirements cannot be demonstrated.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>DE.DP-3</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Detection Processes</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Detection processes are tested.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>No detection use cases, cyber drills or penetration tests.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>DE.DP-4</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Detection Processes</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Event detection information is communicated to appropriate parties.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>No documented communication paths or escalation points for detected events.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DE.DP-5</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Detection Processes</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Detection processes and procedures are maintained and tested to ensure timely and adequate awareness of anomalous events.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Detection processes are continuously improved.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>No lessons-learned or continuous improvement process for detection.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
@@ -3389,202 +4753,607 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>CSF ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>NIST CSF Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Control Objective</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Control (Subcategory)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Finding / Evidence</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Recovery Planning</t>
+          <t>RS.RP-1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Recovery processes and procedures are executed and maintained to ensure timely restoration of systems or assets affected by cybersecurity events.</t>
+          <t>Response Planning</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Recovery plan is executed during or after an event.</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>A documented disaster recovery plan exists and is regularly tested by the IT team.</t>
+          <t>Response processes and procedures are executed and maintained, to ensure timely response to detected cybersecurity events.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Response plan is executed during or after an event.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>No cyber security incident response plan. The analyst responds to incidents 'as they come'.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>E01, E41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Improvements</t>
+          <t>RS.CO-1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Recovery planning and processes are improved by incorporating lessons learned into future activities.</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Recovery plans incorporate lessons learned.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>No evidence of a lessons-learned step in the DR plans. To be added after each test/event.</t>
+          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Personnel know their roles and order of operations when a response is needed.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>No IR plan with contact details and escalation points; nothing tested.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Improvements</t>
+          <t>RS.CO-2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Recovery planning and processes are improved by incorporating lessons learned into future activities.</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Recovery strategies are updated.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>DR plans are tested regularly. Ensure findings lead to documented updates.</t>
+          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Events are reported consistent with established criteria.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>No defined reporting thresholds; incident response process is immature/ad hoc.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>RS.CO-3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>Communications</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Restoration activities are coordinated with internal and external parties, such as coordinating centers, Internet Service Providers, owners of attacking systems, victims, other CSIRTs and vendors.</t>
-        </is>
-      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Public relations are managed.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>DR/BCP plans are IT-owned; no crisis communication / public relations plan.</t>
+          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Information is shared consistent with response plans.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>No escalation points, including when to involve law enforcement.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>RS.CO-4</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>Communications</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Restoration activities are coordinated with internal and external parties, such as coordinating centers, Internet Service Providers, owners of attacking systems, victims, other CSIRTs and vendors.</t>
-        </is>
-      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Reputation after an event is repaired.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>No steps for managing reputational impact after a cyber event.</t>
+          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Coordination with stakeholders occurs consistent with response plans.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>No documented coordination with other teams for escalated incidents.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>RS.CO-5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>Communications</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Restoration activities are coordinated with internal and external parties, such as coordinating centers, Internet Service Providers, owners of attacking systems, victims, other CSIRTs and vendors.</t>
-        </is>
-      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Recovery activities are communicated to internal stakeholders and executive and management teams.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>No clear escalation and communication to executives during recovery (cyber not represented at executive level).</t>
+          <t>Response activities are coordinated with internal and external stakeholders, as appropriate, to include external support from law enforcement agencies.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Voluntary information sharing occurs with external stakeholders to achieve broader cybersecurity situational awareness.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>No voluntary information sharing with industry peers.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>RS.AN-1</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Notifications from detection systems are investigated.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Only antivirus alerts are investigated by IT; no defined process and no 24/7 coverage.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>E42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>RS.AN-2</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>The impact of the incident is understood.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Impact/criticality of incidents is not documented.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>RS.AN-3</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Forensics are performed.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>No digital forensics capability (people, skills or tools).</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>RS.AN-4</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Analysis is conducted to ensure adequate response and support recovery activities.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Incidents are categorized consistent with response plans.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>No IR plan to categorise and prioritise incidents.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>RS.MI-1</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Activities are performed to prevent expansion of an event, mitigate its effects and eradicate the incident.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Incidents are contained.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>No IR plan following a standard (e.g. NIST SP 800-61 / SANS) for containment.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RS.MI-2</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Activities are performed to prevent expansion of an event, mitigate its effects and eradicate the incident.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Incidents are mitigated.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>No IR plan following a standard for mitigation and eradication.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RS.MI-3</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Activities are performed to prevent expansion of an event, mitigate its effects and eradicate the incident.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Newly identified vulnerabilities are mitigated or documented as accepted risk.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>No vulnerability management program to handle newly discovered vulnerabilities (incl. zero days) or document accepted risk.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>RS.IM-1</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Improvements</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Organizational response activities are improved by incorporating lessons learned from current and previous detection/response activities.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Response plans incorporate lessons learned.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>No IR plan, so no lessons-learned step.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>RS.IM-2</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Improvements</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Organizational response activities are improved by incorporating lessons learned from current and previous detection/response activities.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Response strategies are updated.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>No IR plan to test and update.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>E41</t>
         </is>
       </c>
     </row>
@@ -3594,6 +5363,288 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CSF ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>NIST CSF Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Control Objective</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Control (Subcategory)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence Ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>RC.RP-1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Planning</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Recovery processes and procedures are executed and maintained to ensure timely restoration of systems or assets affected by cybersecurity events.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Recovery plan is executed during or after an event.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>A documented disaster recovery plan exists and is regularly tested by the IT team.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RC.IM-1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Improvements</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Recovery planning and processes are improved by incorporating lessons learned into future activities.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Recovery plans incorporate lessons learned.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>No evidence of a lessons-learned step in the DR plans. To be added after each test/event.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>RC.IM-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Improvements</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Recovery planning and processes are improved by incorporating lessons learned into future activities.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Recovery strategies are updated.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>DR plans are tested regularly. Ensure findings lead to documented updates.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>RC.CO-1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Communications</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Restoration activities are coordinated with internal and external parties, such as coordinating centers, Internet Service Providers, owners of attacking systems, victims, other CSIRTs and vendors.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Public relations are managed.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>DR/BCP plans are IT-owned; no crisis communication / public relations plan.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>RC.CO-2</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Communications</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Restoration activities are coordinated with internal and external parties, such as coordinating centers, Internet Service Providers, owners of attacking systems, victims, other CSIRTs and vendors.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Reputation after an event is repaired.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>No steps for managing reputational impact after a cyber event.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>RC.CO-3</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Communications</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Restoration activities are coordinated with internal and external parties, such as coordinating centers, Internet Service Providers, owners of attacking systems, victims, other CSIRTs and vendors.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Recovery activities are communicated to internal stakeholders and executive and management teams.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>No clear escalation and communication to executives during recovery (cyber not represented at executive level).</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>E03, E12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
